--- a/data/regexp.xlsx
+++ b/data/regexp.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kyowapharma-my.sharepoint.com/personal/araya-t_kyowayakuhin_co_jp/Documents/R_scripts/R入門/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{B3E86B85-0BF1-4CCB-83FA-BE27375E3776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{114DD16C-4BFA-4A3C-B52A-4083367A466A}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DFEB583-53B2-4B66-BF68-CACC77E73349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{73AA2973-26F9-40D9-8D7E-D72F95160012}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="16440" xr2:uid="{73AA2973-26F9-40D9-8D7E-D72F95160012}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -614,9 +609,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -654,7 +649,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -760,7 +755,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -902,7 +897,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -911,13 +906,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEA050E5-2A68-4853-815C-0BA69768AC23}">
   <dimension ref="A1:B38"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>52</v>
       </c>
@@ -925,7 +920,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>64</v>
       </c>
@@ -933,7 +928,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
         <v>65</v>
       </c>
@@ -941,7 +936,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
         <v>66</v>
       </c>
@@ -949,7 +944,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
         <v>67</v>
       </c>
@@ -957,7 +952,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
         <v>68</v>
       </c>
@@ -965,7 +960,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
         <v>69</v>
       </c>
@@ -973,7 +968,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
         <v>70</v>
       </c>
@@ -981,7 +976,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
         <v>71</v>
       </c>
@@ -989,7 +984,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>72</v>
       </c>
@@ -997,7 +992,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
         <v>73</v>
       </c>
@@ -1005,7 +1000,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
         <v>74</v>
       </c>
@@ -1013,7 +1008,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -1021,7 +1016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>2</v>
       </c>
@@ -1029,7 +1024,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -1037,7 +1032,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -1045,7 +1040,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -1053,7 +1048,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -1061,7 +1056,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -1069,7 +1064,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -1077,7 +1072,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1085,7 +1080,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -1093,7 +1088,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -1101,7 +1096,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>14</v>
       </c>
@@ -1109,7 +1104,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -1117,7 +1112,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -1125,7 +1120,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -1133,7 +1128,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -1141,7 +1136,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -1149,7 +1144,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -1157,7 +1152,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -1165,7 +1160,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" s="2" t="s">
         <v>41</v>
       </c>
@@ -1173,7 +1168,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>43</v>
       </c>
@@ -1181,7 +1176,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>45</v>
       </c>
@@ -1189,7 +1184,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>47</v>
       </c>
@@ -1197,7 +1192,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>50</v>
       </c>
@@ -1205,7 +1200,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37" s="3" t="s">
         <v>60</v>
       </c>
@@ -1213,7 +1208,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" s="3" t="s">
         <v>62</v>
       </c>
@@ -1236,5 +1231,6 @@
     <hyperlink ref="A12" r:id="rId10" xr:uid="{E99B9969-1603-4529-9FCD-76D9ADE584F9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId11"/>
 </worksheet>
 </file>